--- a/research/traditional_assets/database/data/canada/canada_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ13"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.2785</v>
-      </c>
-      <c r="E2">
-        <v>0.657</v>
+        <v>0.128</v>
       </c>
       <c r="G2">
-        <v>0.0100507495653417</v>
+        <v>-0.1973170731707317</v>
       </c>
       <c r="H2">
-        <v>-0.004745250470900797</v>
+        <v>-0.1973170731707317</v>
       </c>
       <c r="I2">
-        <v>-0.001271507657737925</v>
+        <v>-0.9633333333333333</v>
       </c>
       <c r="J2">
-        <v>-0.001228706470439518</v>
+        <v>-0.9633333333333333</v>
       </c>
       <c r="K2">
-        <v>281.097</v>
+        <v>-19.33</v>
       </c>
       <c r="L2">
-        <v>0.1414952446821684</v>
+        <v>-1.571544715447154</v>
       </c>
       <c r="M2">
-        <v>149.193</v>
+        <v>1.077</v>
       </c>
       <c r="N2">
-        <v>0.09886223576966403</v>
+        <v>0.02560019015925838</v>
       </c>
       <c r="O2">
-        <v>0.5307527294848398</v>
+        <v>-0.05571650284531816</v>
       </c>
       <c r="P2">
-        <v>22.915</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="Q2">
-        <v>0.01518454708104168</v>
+        <v>0.01972902305681008</v>
       </c>
       <c r="R2">
-        <v>0.08151990238245162</v>
+        <v>-0.04293843766166582</v>
       </c>
       <c r="S2">
-        <v>126.278</v>
+        <v>0.247</v>
       </c>
       <c r="T2">
-        <v>0.8464070030095246</v>
+        <v>0.2293407613741876</v>
       </c>
       <c r="U2">
-        <v>1821.555</v>
+        <v>5.094</v>
       </c>
       <c r="V2">
-        <v>1.207047246703333</v>
+        <v>0.1210839077727597</v>
       </c>
       <c r="W2">
-        <v>0.3098591549295775</v>
+        <v>-0.4090425531914894</v>
       </c>
       <c r="X2">
-        <v>0.03343315060065588</v>
+        <v>0.07122778616133035</v>
       </c>
       <c r="Y2">
-        <v>0.2764260043289216</v>
+        <v>-0.4802703393528197</v>
       </c>
       <c r="Z2">
-        <v>-9.294554131187427</v>
+        <v>0.2080232715464755</v>
       </c>
       <c r="AA2">
-        <v>-0</v>
+        <v>-0.1079079079079079</v>
       </c>
       <c r="AB2">
-        <v>0.03335508623995292</v>
+        <v>0.06579141120325535</v>
       </c>
       <c r="AC2">
-        <v>-0.03342571746529402</v>
+        <v>-0.1885873928666172</v>
       </c>
       <c r="AD2">
-        <v>355.352</v>
+        <v>26.73</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>355.352</v>
+        <v>26.73</v>
       </c>
       <c r="AG2">
-        <v>-1466.203</v>
+        <v>21.636</v>
       </c>
       <c r="AH2">
-        <v>0.1905932681560051</v>
+        <v>0.3885174418604652</v>
       </c>
       <c r="AI2">
-        <v>0.1999247227315409</v>
+        <v>0.5103677397181808</v>
       </c>
       <c r="AJ2">
-        <v>-34.17961629018352</v>
+        <v>0.3396226415094339</v>
       </c>
       <c r="AK2">
-        <v>33.22764356615149</v>
+        <v>0.4576142131979695</v>
       </c>
       <c r="AL2">
-        <v>0.206</v>
+        <v>0.216</v>
       </c>
       <c r="AM2">
-        <v>0.02800000000000002</v>
+        <v>0.213</v>
       </c>
       <c r="AN2">
-        <v>-174.7059980334317</v>
+        <v>-14.60655737704918</v>
       </c>
       <c r="AO2">
-        <v>-12.2621359223301</v>
+        <v>-54.85648148148148</v>
       </c>
       <c r="AP2">
-        <v>720.847099311701</v>
+        <v>-11.82295081967213</v>
       </c>
       <c r="AQ2">
-        <v>-90.21428571428567</v>
+        <v>-55.62910798122066</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Digatrade Financial Corp. (OTCPK:DIGA.F)</t>
+          <t>Fountain Asset Corp. (TSXV:FA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,7 +719,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-1.7</v>
+        <v>-7.69</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,67 +743,61 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.027</v>
+        <v>1.01</v>
       </c>
       <c r="V3">
-        <v>0.004615384615384616</v>
+        <v>0.1578125</v>
       </c>
       <c r="W3">
-        <v>7.391304347826086</v>
+        <v>-0.4090425531914894</v>
       </c>
       <c r="X3">
-        <v>0.03343315060065588</v>
+        <v>0.06579141120325535</v>
       </c>
       <c r="Y3">
-        <v>7.35787119722543</v>
+        <v>-0.4748339643947447</v>
       </c>
       <c r="Z3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>6.53968253968254</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03386813520058389</v>
+        <v>0.06579141120325535</v>
       </c>
       <c r="AC3">
-        <v>6.505814404481955</v>
+        <v>-0.06579141120325535</v>
       </c>
       <c r="AD3">
-        <v>0.074</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.074</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.047</v>
+        <v>-1.01</v>
       </c>
       <c r="AH3">
-        <v>0.012491559756921</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>-0.3699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.007970154315753774</v>
+        <v>-0.1873840445269017</v>
       </c>
       <c r="AK3">
-        <v>-0.2070484581497797</v>
+        <v>-0.1160919540229885</v>
       </c>
       <c r="AL3">
-        <v>0.164</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.164</v>
-      </c>
-      <c r="AO3">
-        <v>-2.512195121951219</v>
-      </c>
-      <c r="AQ3">
-        <v>-2.512195121951219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -817,7 +808,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Strategem Capital Corporation (TSXV:SGE)</t>
+          <t>Hampton Financial Corporation (TSXV:HFC)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -826,10 +817,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.323</v>
-      </c>
-      <c r="E4">
-        <v>0.0206</v>
+        <v>0.128</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -838,88 +826,91 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.8563432835820894</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>0.8563432835820894</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>3.75</v>
+        <v>1.33</v>
       </c>
       <c r="L4">
-        <v>0.6996268656716418</v>
+        <v>0.108130081300813</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>0.467</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.02847560975609757</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.3511278195488722</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>0.467</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.02847560975609757</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.3511278195488722</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>3.83</v>
+        <v>3.2</v>
       </c>
       <c r="V4">
-        <v>0.1886699507389163</v>
+        <v>0.1951219512195122</v>
       </c>
       <c r="W4">
-        <v>0.4427390791027154</v>
+        <v>-1.015267175572519</v>
       </c>
       <c r="X4">
-        <v>0.03326426946963817</v>
+        <v>0.07887566236580901</v>
       </c>
       <c r="Y4">
-        <v>0.4094748096330773</v>
+        <v>-1.094142837938328</v>
       </c>
       <c r="Z4">
-        <v>3.01123595505618</v>
+        <v>2.821100917431193</v>
       </c>
       <c r="AA4">
-        <v>2.578651685393258</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.03326426946963817</v>
+        <v>0.09340132825182473</v>
       </c>
       <c r="AC4">
-        <v>2.54538741592362</v>
+        <v>-0.09340132825182473</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="AG4">
-        <v>-3.83</v>
+        <v>7.399999999999999</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.3925925925925926</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1.031730582051781</v>
       </c>
       <c r="AJ4">
-        <v>-0.2325440194292654</v>
+        <v>0.3109243697478992</v>
       </c>
       <c r="AK4">
-        <v>-0.2119535141117875</v>
+        <v>1.046084252191122</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -936,7 +927,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quinsam Capital Corporation (CNSX:QCA)</t>
+          <t>GreenBank Capital Inc. (OTCPK:GRNB.F)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -944,110 +935,92 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.628</v>
-      </c>
-      <c r="E5">
-        <v>0.657</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0.8025974025974025</v>
-      </c>
-      <c r="J5">
-        <v>0.7885714285714285</v>
-      </c>
       <c r="K5">
-        <v>3.04</v>
-      </c>
-      <c r="L5">
-        <v>0.7896103896103897</v>
+        <v>-4.51</v>
       </c>
       <c r="M5">
-        <v>1.224</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.1055172413793103</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.4026315789473684</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.415</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.03577586206896552</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.1365131578947368</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>0.8089999999999999</v>
-      </c>
-      <c r="T5">
-        <v>0.6609477124183006</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>0.221</v>
+        <v>0.094</v>
       </c>
       <c r="V5">
-        <v>0.01905172413793103</v>
+        <v>0.007580645161290323</v>
       </c>
       <c r="W5">
-        <v>0.1235772357723577</v>
+        <v>-2.157894736842105</v>
       </c>
       <c r="X5">
-        <v>0.03326426946963817</v>
+        <v>0.07122778616133035</v>
       </c>
       <c r="Y5">
-        <v>0.09031296630271954</v>
+        <v>-2.229122523003435</v>
       </c>
       <c r="Z5">
-        <v>0.1585406028660847</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>0.1250205896886839</v>
+        <v>-0.1079079079079079</v>
       </c>
       <c r="AB5">
-        <v>0.03326426946963817</v>
+        <v>0.08067948495870925</v>
       </c>
       <c r="AC5">
-        <v>0.09175632021904573</v>
+        <v>-0.1885873928666172</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AG5">
-        <v>-0.221</v>
+        <v>3.236</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.2116973935155753</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>0.3248780487804878</v>
       </c>
       <c r="AJ5">
-        <v>-0.01942174180507953</v>
+        <v>0.2069583013558455</v>
       </c>
       <c r="AK5">
-        <v>-0.007927113598048711</v>
+        <v>0.3186293816463174</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.216</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>0.216</v>
+      </c>
+      <c r="AO5">
+        <v>-2.495370370370371</v>
+      </c>
+      <c r="AQ5">
+        <v>-2.495370370370371</v>
       </c>
     </row>
     <row r="6">
@@ -1058,7 +1031,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Canaccord Genuity Group Inc. (TSX:CF)</t>
+          <t>Quinsam Capital Corporation (CNSX:QCA)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1066,101 +1039,83 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.234</v>
-      </c>
-      <c r="G6">
-        <v>0.01625923169405164</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
       <c r="K6">
-        <v>263.7</v>
-      </c>
-      <c r="L6">
-        <v>0.1509704013282189</v>
+        <v>-9.6</v>
       </c>
       <c r="M6">
-        <v>110.3</v>
+        <v>0.61</v>
       </c>
       <c r="N6">
-        <v>0.09841184867951464</v>
+        <v>0.1055363321799308</v>
       </c>
       <c r="O6">
-        <v>0.4182783466059917</v>
+        <v>-0.06354166666666666</v>
       </c>
       <c r="P6">
-        <v>22.5</v>
+        <v>0.363</v>
       </c>
       <c r="Q6">
-        <v>0.02007494646680942</v>
+        <v>0.06280276816608996</v>
       </c>
       <c r="R6">
-        <v>0.08532423208191127</v>
+        <v>-0.0378125</v>
       </c>
       <c r="S6">
-        <v>87.8</v>
+        <v>0.247</v>
       </c>
       <c r="T6">
-        <v>0.7960108794197642</v>
+        <v>0.4049180327868853</v>
       </c>
       <c r="U6">
-        <v>1364.5</v>
+        <v>0.79</v>
       </c>
       <c r="V6">
-        <v>1.21743397573162</v>
+        <v>0.1366782006920415</v>
       </c>
       <c r="W6">
-        <v>0.4812922066070451</v>
+        <v>-0.3416370106761565</v>
       </c>
       <c r="X6">
-        <v>0.03597182011299991</v>
+        <v>0.06579141120325535</v>
       </c>
       <c r="Y6">
-        <v>0.4453203864940452</v>
+        <v>-0.4074284218794119</v>
       </c>
       <c r="Z6">
-        <v>-64.21691176470604</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>-0</v>
+        <v>-0.3396821980702321</v>
       </c>
       <c r="AB6">
-        <v>0.03279990058099964</v>
+        <v>0.06579141120325535</v>
       </c>
       <c r="AC6">
-        <v>-0.03279990058099964</v>
+        <v>-0.4054736092734874</v>
       </c>
       <c r="AD6">
-        <v>227.3</v>
+        <v>0</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>227.3</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>-1137.2</v>
+        <v>-0.79</v>
       </c>
       <c r="AH6">
-        <v>0.1686076700541503</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>0.1744971595270997</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>69.34146341463376</v>
+        <v>-0.1583166332665331</v>
       </c>
       <c r="AK6">
-        <v>18.37156704361871</v>
+        <v>-0.05298457411133468</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1177,7 +1132,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fountain Asset Corp. (TSXV:FA)</t>
+          <t>Magnetic North Acquisition Corp. (TSXV:MNC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1185,29 +1140,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.479</v>
-      </c>
-      <c r="E7">
-        <v>1.168</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
       <c r="K7">
-        <v>7.08</v>
-      </c>
-      <c r="L7">
-        <v>0.9528936742934052</v>
+        <v>1.14</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1231,763 +1165,70 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>0.07792207792207792</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>0.6742857142857143</v>
+        <v>-0.1341176470588235</v>
       </c>
       <c r="X7">
-        <v>0.03326426946963817</v>
+        <v>0.3035139318924768</v>
       </c>
       <c r="Y7">
-        <v>0.6410214448160761</v>
+        <v>-0.4376315789513003</v>
       </c>
       <c r="Z7">
-        <v>0.7443398116609898</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>-0.4285048905449464</v>
       </c>
       <c r="AB7">
-        <v>0.03326426946963817</v>
+        <v>0.0644571768007775</v>
       </c>
       <c r="AC7">
-        <v>-0.03326426946963817</v>
+        <v>-0.4929620673457239</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="AG7">
-        <v>-1.2</v>
+        <v>12.8</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>0.9215262778977682</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1.987577639751553</v>
       </c>
       <c r="AJ7">
-        <v>-0.08450704225352111</v>
+        <v>0.9215262778977682</v>
       </c>
       <c r="AK7">
-        <v>-0.06818181818181818</v>
+        <v>1.987577639751553</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>DelphX Capital Markets Inc. (TSXV:DELX)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="G8">
-        <v>-0.8928571428571429</v>
-      </c>
-      <c r="H8">
-        <v>-0</v>
-      </c>
-      <c r="I8">
-        <v>-0</v>
-      </c>
-      <c r="J8">
-        <v>-0</v>
-      </c>
-      <c r="K8">
-        <v>-2.64</v>
-      </c>
-      <c r="L8">
-        <v>23.57142857142857</v>
-      </c>
-      <c r="M8">
-        <v>-0</v>
-      </c>
-      <c r="N8">
-        <v>-0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>-0</v>
-      </c>
-      <c r="Q8">
-        <v>-0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>1.61</v>
-      </c>
-      <c r="V8">
-        <v>0.03788235294117647</v>
-      </c>
-      <c r="W8">
-        <v>0.9635036496350364</v>
-      </c>
-      <c r="X8">
-        <v>0.03335065659826289</v>
-      </c>
-      <c r="Y8">
-        <v>0.9301529930367736</v>
-      </c>
-      <c r="Z8">
-        <v>0.05135259055479138</v>
-      </c>
-      <c r="AA8">
-        <v>-0</v>
-      </c>
-      <c r="AB8">
-        <v>0.03342571746529402</v>
-      </c>
-      <c r="AC8">
-        <v>-0.03342571746529402</v>
-      </c>
-      <c r="AD8">
-        <v>0.275</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>0.275</v>
-      </c>
-      <c r="AG8">
-        <v>-1.335</v>
-      </c>
-      <c r="AH8">
-        <v>0.006428988895382817</v>
-      </c>
-      <c r="AI8">
-        <v>-1.580459770114943</v>
-      </c>
-      <c r="AJ8">
-        <v>-0.03243046277177214</v>
-      </c>
-      <c r="AK8">
-        <v>0.7483183856502242</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>RF Capital Group Inc. (TSX:RCG)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>0.112</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>17.6</v>
-      </c>
-      <c r="L9">
-        <v>0.08337280909521555</v>
-      </c>
-      <c r="M9">
-        <v>34.4</v>
-      </c>
-      <c r="N9">
-        <v>0.1455776555226407</v>
-      </c>
-      <c r="O9">
-        <v>1.954545454545454</v>
-      </c>
-      <c r="P9">
-        <v>-0</v>
-      </c>
-      <c r="Q9">
-        <v>-0</v>
-      </c>
-      <c r="R9">
-        <v>-0</v>
-      </c>
-      <c r="S9">
-        <v>34.4</v>
-      </c>
-      <c r="T9">
-        <v>1</v>
-      </c>
-      <c r="U9">
-        <v>445.7</v>
-      </c>
-      <c r="V9">
-        <v>1.886161658908167</v>
-      </c>
-      <c r="W9">
-        <v>0.3098591549295775</v>
-      </c>
-      <c r="X9">
-        <v>0.03928142394873085</v>
-      </c>
-      <c r="Y9">
-        <v>0.2705777309808466</v>
-      </c>
-      <c r="Z9">
-        <v>-0.9378054198134163</v>
-      </c>
-      <c r="AA9">
-        <v>-0</v>
-      </c>
-      <c r="AB9">
-        <v>0.03346309061874892</v>
-      </c>
-      <c r="AC9">
-        <v>-0.03346309061874892</v>
-      </c>
-      <c r="AD9">
-        <v>106.5</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>106.5</v>
-      </c>
-      <c r="AG9">
-        <v>-339.2</v>
-      </c>
-      <c r="AH9">
-        <v>0.3106767794632438</v>
-      </c>
-      <c r="AI9">
-        <v>0.2734274711168164</v>
-      </c>
-      <c r="AJ9">
-        <v>3.296404275996113</v>
-      </c>
-      <c r="AK9">
-        <v>6.035587188612101</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Hampton Financial Corporation (TSXV:HFC)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>0.179</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>1.02</v>
-      </c>
-      <c r="L10">
-        <v>0.08717948717948719</v>
-      </c>
-      <c r="M10">
-        <v>0.079</v>
-      </c>
-      <c r="N10">
-        <v>0.006583333333333333</v>
-      </c>
-      <c r="O10">
-        <v>0.07745098039215687</v>
-      </c>
-      <c r="P10">
-        <v>-0</v>
-      </c>
-      <c r="Q10">
-        <v>-0</v>
-      </c>
-      <c r="R10">
-        <v>-0</v>
-      </c>
-      <c r="S10">
-        <v>0.079</v>
-      </c>
-      <c r="T10">
-        <v>1</v>
-      </c>
-      <c r="U10">
-        <v>1.75</v>
-      </c>
-      <c r="V10">
-        <v>0.1458333333333333</v>
-      </c>
-      <c r="W10">
-        <v>-0.4232365145228216</v>
-      </c>
-      <c r="X10">
-        <v>0.04151947583685198</v>
-      </c>
-      <c r="Y10">
-        <v>-0.4647559903596735</v>
-      </c>
-      <c r="Z10">
-        <v>3.735632183908046</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>0.05173475850205702</v>
-      </c>
-      <c r="AC10">
-        <v>-0.05173475850205702</v>
-      </c>
-      <c r="AD10">
-        <v>7.42</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>7.42</v>
-      </c>
-      <c r="AG10">
-        <v>5.67</v>
-      </c>
-      <c r="AH10">
-        <v>0.3820803295571575</v>
-      </c>
-      <c r="AI10">
-        <v>1.214402618657938</v>
-      </c>
-      <c r="AJ10">
-        <v>0.3208828522920203</v>
-      </c>
-      <c r="AK10">
-        <v>1.300458715596331</v>
-      </c>
-      <c r="AL10">
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>IC Capitalight Corp. (CNSX:IC)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="G11">
-        <v>-0.6666666666666665</v>
-      </c>
-      <c r="H11">
-        <v>-1.993127147766323</v>
-      </c>
-      <c r="I11">
-        <v>-2.350515463917526</v>
-      </c>
-      <c r="J11">
-        <v>-2.350515463917526</v>
-      </c>
-      <c r="K11">
-        <v>0.277</v>
-      </c>
-      <c r="L11">
-        <v>0.9518900343642613</v>
-      </c>
-      <c r="M11">
-        <v>-0</v>
-      </c>
-      <c r="N11">
-        <v>-0</v>
-      </c>
-      <c r="O11">
-        <v>-0</v>
-      </c>
-      <c r="P11">
-        <v>-0</v>
-      </c>
-      <c r="Q11">
-        <v>-0</v>
-      </c>
-      <c r="R11">
-        <v>-0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0.221</v>
-      </c>
-      <c r="V11">
-        <v>0.03463949843260188</v>
-      </c>
-      <c r="W11">
-        <v>0.2429824561403509</v>
-      </c>
-      <c r="X11">
-        <v>0.03333123241915634</v>
-      </c>
-      <c r="Y11">
-        <v>0.2096512237211946</v>
-      </c>
-      <c r="Z11">
-        <v>0.3102345415778252</v>
-      </c>
-      <c r="AA11">
-        <v>-0.7292110874200428</v>
-      </c>
-      <c r="AB11">
-        <v>0.03327863903795814</v>
-      </c>
-      <c r="AC11">
-        <v>-0.7624897264580009</v>
-      </c>
-      <c r="AD11">
-        <v>0.032</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>0.032</v>
-      </c>
-      <c r="AG11">
-        <v>-0.189</v>
-      </c>
-      <c r="AH11">
-        <v>0.004990642545227698</v>
-      </c>
-      <c r="AI11">
-        <v>0.01606425702811245</v>
-      </c>
-      <c r="AJ11">
-        <v>-0.03052818607656275</v>
-      </c>
-      <c r="AK11">
-        <v>-0.1067193675889328</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>-0.156</v>
-      </c>
-      <c r="AN11">
-        <v>-0.04747774480712166</v>
-      </c>
-      <c r="AP11">
-        <v>0.2804154302670623</v>
-      </c>
-      <c r="AQ11">
-        <v>4.384615384615385</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>GreenBank Capital Inc. (OTCPK:GRNB.F)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="G12">
-        <v>-16.15686274509804</v>
-      </c>
-      <c r="H12">
-        <v>-16.2156862745098</v>
-      </c>
-      <c r="I12">
-        <v>-26.07843137254902</v>
-      </c>
-      <c r="J12">
-        <v>-26.07843137254902</v>
-      </c>
-      <c r="K12">
-        <v>-1.83</v>
-      </c>
-      <c r="L12">
-        <v>-35.88235294117647</v>
-      </c>
-      <c r="M12">
-        <v>-0</v>
-      </c>
-      <c r="N12">
-        <v>-0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>-0</v>
-      </c>
-      <c r="Q12">
-        <v>-0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>2.49</v>
-      </c>
-      <c r="V12">
-        <v>0.08527397260273974</v>
-      </c>
-      <c r="W12">
-        <v>-4.093959731543624</v>
-      </c>
-      <c r="X12">
-        <v>0.03369908289070787</v>
-      </c>
-      <c r="Y12">
-        <v>-4.127658814434332</v>
-      </c>
-      <c r="Z12">
-        <v>0.07412790697674419</v>
-      </c>
-      <c r="AA12">
-        <v>-1.933139534883721</v>
-      </c>
-      <c r="AB12">
-        <v>0.03335508623995292</v>
-      </c>
-      <c r="AC12">
-        <v>-1.966494621123674</v>
-      </c>
-      <c r="AD12">
-        <v>0.951</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>0.951</v>
-      </c>
-      <c r="AG12">
-        <v>-1.539</v>
-      </c>
-      <c r="AH12">
-        <v>0.03154124241318696</v>
-      </c>
-      <c r="AI12">
-        <v>0.2112863808042657</v>
-      </c>
-      <c r="AJ12">
-        <v>-0.05563790173891039</v>
-      </c>
-      <c r="AK12">
-        <v>-0.7652909000497267</v>
-      </c>
-      <c r="AL12">
-        <v>0.042</v>
-      </c>
-      <c r="AM12">
-        <v>0.042</v>
-      </c>
-      <c r="AN12">
-        <v>-0.6992647058823529</v>
-      </c>
-      <c r="AO12">
-        <v>-31.66666666666667</v>
-      </c>
-      <c r="AP12">
-        <v>1.131617647058824</v>
-      </c>
-      <c r="AQ12">
-        <v>-31.66666666666667</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Magnetic North Acquisition Corp. (TSXV:MNC)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="G13">
-        <v>-30.30241935483871</v>
-      </c>
-      <c r="H13">
-        <v>-32.33870967741935</v>
-      </c>
-      <c r="I13">
-        <v>-31.37096774193548</v>
-      </c>
-      <c r="J13">
-        <v>-31.37096774193548</v>
-      </c>
-      <c r="K13">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="L13">
-        <v>-37.09677419354838</v>
-      </c>
-      <c r="M13">
-        <v>3.19</v>
-      </c>
-      <c r="N13">
-        <v>0.3637400228050171</v>
-      </c>
-      <c r="O13">
-        <v>-0.3467391304347826</v>
-      </c>
-      <c r="P13">
-        <v>-0</v>
-      </c>
-      <c r="Q13">
-        <v>-0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>3.19</v>
-      </c>
-      <c r="T13">
-        <v>1</v>
-      </c>
-      <c r="U13">
-        <v>0.006</v>
-      </c>
-      <c r="V13">
-        <v>0.0006841505131128849</v>
-      </c>
-      <c r="X13">
-        <v>0.05274995329750087</v>
-      </c>
-      <c r="AB13">
-        <v>0.06195116415167101</v>
-      </c>
-      <c r="AD13">
-        <v>12.8</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>12.8</v>
-      </c>
-      <c r="AG13">
-        <v>12.794</v>
-      </c>
-      <c r="AH13">
-        <v>0.593416782568382</v>
-      </c>
-      <c r="AI13">
-        <v>2.976744186046511</v>
-      </c>
-      <c r="AJ13">
-        <v>0.5933036542385457</v>
-      </c>
-      <c r="AK13">
-        <v>2.979506287843502</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>-0.022</v>
-      </c>
-      <c r="AQ13">
-        <v>353.6363636363637</v>
+        <v>-0.003</v>
+      </c>
+      <c r="AN7">
+        <v>-6.994535519125683</v>
+      </c>
+      <c r="AP7">
+        <v>-6.994535519125683</v>
+      </c>
+      <c r="AQ7">
+        <v>613.3333333333334</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/canada/canada_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,118 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.128</v>
+        <v>-0.1</v>
       </c>
       <c r="G2">
-        <v>-0.1973170731707317</v>
+        <v>-0.8224314502808061</v>
       </c>
       <c r="H2">
-        <v>-0.1973170731707317</v>
+        <v>-0.9142715559960357</v>
       </c>
       <c r="I2">
-        <v>-0.9633333333333333</v>
+        <v>-1.995540138751239</v>
       </c>
       <c r="J2">
-        <v>-0.9633333333333333</v>
+        <v>-1.995540138751239</v>
       </c>
       <c r="K2">
-        <v>-19.33</v>
+        <v>-22.086</v>
       </c>
       <c r="L2">
-        <v>-1.571544715447154</v>
+        <v>-3.64816650148662</v>
       </c>
       <c r="M2">
-        <v>1.077</v>
+        <v>1.04</v>
       </c>
       <c r="N2">
-        <v>0.02560019015925838</v>
+        <v>0.03686635944700461</v>
       </c>
       <c r="O2">
-        <v>-0.05571650284531816</v>
+        <v>-0.04708865344562166</v>
       </c>
       <c r="P2">
-        <v>0.8300000000000001</v>
+        <v>0.632</v>
       </c>
       <c r="Q2">
-        <v>0.01972902305681008</v>
+        <v>0.02240340304856434</v>
       </c>
       <c r="R2">
-        <v>-0.04293843766166582</v>
+        <v>-0.02861541247849316</v>
       </c>
       <c r="S2">
-        <v>0.247</v>
+        <v>0.408</v>
       </c>
       <c r="T2">
-        <v>0.2293407613741876</v>
+        <v>0.3923076923076923</v>
       </c>
       <c r="U2">
-        <v>5.094</v>
+        <v>3.249</v>
       </c>
       <c r="V2">
-        <v>0.1210839077727597</v>
+        <v>0.1151719248493442</v>
       </c>
       <c r="W2">
-        <v>-0.4090425531914894</v>
+        <v>-0.243048403707518</v>
       </c>
       <c r="X2">
-        <v>0.07122778616133035</v>
+        <v>0.05679181795512367</v>
       </c>
       <c r="Y2">
-        <v>-0.4802703393528197</v>
+        <v>-0.2998402216626417</v>
       </c>
       <c r="Z2">
-        <v>0.2080232715464755</v>
+        <v>0.12449105490438</v>
       </c>
       <c r="AA2">
-        <v>-0.1079079079079079</v>
+        <v>-0.1842948717948718</v>
       </c>
       <c r="AB2">
-        <v>0.06579141120325535</v>
+        <v>0.05655055051795606</v>
       </c>
       <c r="AC2">
-        <v>-0.1885873928666172</v>
+        <v>-0.2409031974228474</v>
       </c>
       <c r="AD2">
-        <v>26.73</v>
+        <v>25.59</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>26.73</v>
+        <v>25.59</v>
       </c>
       <c r="AG2">
-        <v>21.636</v>
+        <v>22.341</v>
       </c>
       <c r="AH2">
-        <v>0.3885174418604652</v>
+        <v>0.4756505576208179</v>
       </c>
       <c r="AI2">
-        <v>0.5103677397181808</v>
+        <v>0.5821201091901729</v>
       </c>
       <c r="AJ2">
-        <v>0.3396226415094339</v>
+        <v>0.4419497141500663</v>
       </c>
       <c r="AK2">
-        <v>0.4576142131979695</v>
+        <v>0.5487706025398541</v>
       </c>
       <c r="AL2">
-        <v>0.216</v>
+        <v>0.209</v>
       </c>
       <c r="AM2">
-        <v>0.213</v>
+        <v>-1.153</v>
       </c>
       <c r="AN2">
-        <v>-14.60655737704918</v>
+        <v>-6.079828937990022</v>
       </c>
       <c r="AO2">
-        <v>-54.85648148148148</v>
+        <v>-57.80382775119617</v>
       </c>
       <c r="AP2">
-        <v>-11.82295081967213</v>
+        <v>-5.307911617961512</v>
       </c>
       <c r="AQ2">
-        <v>-55.62910798122066</v>
+        <v>10.47788378143972</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fountain Asset Corp. (TSXV:FA)</t>
+          <t>Hampton Financial Corporation (TSXV:HFC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -718,80 +718,101 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D3">
+        <v>-0.1</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
       <c r="K3">
-        <v>-7.69</v>
+        <v>-2.16</v>
+      </c>
+      <c r="L3">
+        <v>-0.3898916967509026</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.451</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.03758333333333334</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.2087962962962963</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.451</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.03758333333333334</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0.2087962962962963</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>0.372</v>
       </c>
       <c r="V3">
-        <v>0.1578125</v>
+        <v>0.031</v>
       </c>
       <c r="W3">
-        <v>-0.4090425531914894</v>
+        <v>6.625766871165644</v>
       </c>
       <c r="X3">
-        <v>0.06579141120325535</v>
+        <v>0.06634881193426721</v>
       </c>
       <c r="Y3">
-        <v>-0.4748339643947447</v>
+        <v>6.559418059231377</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>0.7831495617755161</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06579141120325535</v>
+        <v>0.05482528396613505</v>
       </c>
       <c r="AC3">
-        <v>-0.06579141120325535</v>
+        <v>-0.05482528396613505</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>8.93</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>8.93</v>
       </c>
       <c r="AG3">
-        <v>-1.01</v>
+        <v>8.558</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.4266602962255136</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>1.375963020030817</v>
       </c>
       <c r="AJ3">
-        <v>-0.1873840445269017</v>
+        <v>0.4162856308979473</v>
       </c>
       <c r="AK3">
-        <v>-0.1160919540229885</v>
+        <v>1.398823144818568</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -808,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hampton Financial Corporation (TSXV:HFC)</t>
+          <t>Fountain Asset Corp. (TSXV:FA)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -816,101 +837,80 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.128</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
       <c r="K4">
-        <v>1.33</v>
-      </c>
-      <c r="L4">
-        <v>0.108130081300813</v>
+        <v>-2.36</v>
       </c>
       <c r="M4">
-        <v>0.467</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.02847560975609757</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.3511278195488722</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>0.467</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.02847560975609757</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.3511278195488722</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>3.2</v>
+        <v>0.347</v>
       </c>
       <c r="V4">
-        <v>0.1951219512195122</v>
+        <v>0.1137704918032787</v>
       </c>
       <c r="W4">
-        <v>-1.015267175572519</v>
+        <v>-0.243048403707518</v>
       </c>
       <c r="X4">
-        <v>0.07887566236580901</v>
+        <v>0.0566083256279756</v>
       </c>
       <c r="Y4">
-        <v>-1.094142837938328</v>
+        <v>-0.2996567293354936</v>
       </c>
       <c r="Z4">
-        <v>2.821100917431193</v>
+        <v>0</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.09340132825182473</v>
+        <v>0.0566083256279756</v>
       </c>
       <c r="AC4">
-        <v>-0.09340132825182473</v>
+        <v>-0.0566083256279756</v>
       </c>
       <c r="AD4">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>7.399999999999999</v>
+        <v>-0.347</v>
       </c>
       <c r="AH4">
-        <v>0.3925925925925926</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>1.031730582051781</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0.3109243697478992</v>
+        <v>-0.1283758786533481</v>
       </c>
       <c r="AK4">
-        <v>1.046084252191122</v>
+        <v>-0.04790832527958028</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="K5">
-        <v>-4.51</v>
+        <v>-2.96</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -960,67 +960,67 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.094</v>
+        <v>0.092</v>
       </c>
       <c r="V5">
-        <v>0.007580645161290323</v>
+        <v>0.146031746031746</v>
       </c>
       <c r="W5">
-        <v>-2.157894736842105</v>
+        <v>-1.691428571428572</v>
       </c>
       <c r="X5">
-        <v>0.07122778616133035</v>
+        <v>0.1320265846624523</v>
       </c>
       <c r="Y5">
-        <v>-2.229122523003435</v>
+        <v>-1.823455156091024</v>
       </c>
       <c r="Z5">
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>-0.1079079079079079</v>
+        <v>-0.147170527914926</v>
       </c>
       <c r="AB5">
-        <v>0.08067948495870925</v>
+        <v>0.05304729026698239</v>
       </c>
       <c r="AC5">
-        <v>-0.1885873928666172</v>
+        <v>-0.2002178181819084</v>
       </c>
       <c r="AD5">
-        <v>3.33</v>
+        <v>3.63</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>3.33</v>
+        <v>3.63</v>
       </c>
       <c r="AG5">
-        <v>3.236</v>
+        <v>3.538</v>
       </c>
       <c r="AH5">
-        <v>0.2116973935155753</v>
+        <v>0.852112676056338</v>
       </c>
       <c r="AI5">
-        <v>0.3248780487804878</v>
+        <v>0.2941653160453809</v>
       </c>
       <c r="AJ5">
-        <v>0.2069583013558455</v>
+        <v>0.8488483685220729</v>
       </c>
       <c r="AK5">
-        <v>0.3186293816463174</v>
+        <v>0.2888634879163945</v>
       </c>
       <c r="AL5">
-        <v>0.216</v>
+        <v>0.209</v>
       </c>
       <c r="AM5">
-        <v>0.216</v>
+        <v>-1.071</v>
       </c>
       <c r="AO5">
-        <v>-2.495370370370371</v>
+        <v>-3.708133971291866</v>
       </c>
       <c r="AQ5">
-        <v>-2.495370370370371</v>
+        <v>0.723622782446312</v>
       </c>
     </row>
     <row r="6">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Quinsam Capital Corporation (CNSX:QCA)</t>
+          <t>Strategem Capital Corporation (TSXV:SGE)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1040,58 +1040,55 @@
         </is>
       </c>
       <c r="K6">
-        <v>-9.6</v>
+        <v>-1.17</v>
       </c>
       <c r="M6">
-        <v>0.61</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.1055363321799308</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>-0.06354166666666666</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0.363</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.06280276816608996</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>-0.0378125</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>0.247</v>
-      </c>
-      <c r="T6">
-        <v>0.4049180327868853</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>0.79</v>
+        <v>0.218</v>
       </c>
       <c r="V6">
-        <v>0.1366782006920415</v>
+        <v>0.06318840579710144</v>
       </c>
       <c r="W6">
-        <v>-0.3416370106761565</v>
+        <v>-0.1404561824729892</v>
       </c>
       <c r="X6">
-        <v>0.06579141120325535</v>
+        <v>0.0566083256279756</v>
       </c>
       <c r="Y6">
-        <v>-0.4074284218794119</v>
+        <v>-0.1970645081009648</v>
       </c>
       <c r="Z6">
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>-0.3396821980702321</v>
+        <v>-0.1842948717948718</v>
       </c>
       <c r="AB6">
-        <v>0.06579141120325535</v>
+        <v>0.0566083256279756</v>
       </c>
       <c r="AC6">
-        <v>-0.4054736092734874</v>
+        <v>-0.2409031974228474</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1103,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>-0.79</v>
+        <v>-0.218</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -1112,10 +1109,10 @@
         <v>0</v>
       </c>
       <c r="AJ6">
-        <v>-0.1583166332665331</v>
+        <v>-0.06745049504950494</v>
       </c>
       <c r="AK6">
-        <v>-0.05298457411133468</v>
+        <v>-0.03122314523059295</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1132,103 +1129,320 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Quinsam Capital Corporation (CNSX:QCA)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="K7">
+        <v>-5.4</v>
+      </c>
+      <c r="M7">
+        <v>0.267</v>
+      </c>
+      <c r="N7">
+        <v>0.0662531017369727</v>
+      </c>
+      <c r="O7">
+        <v>-0.04944444444444444</v>
+      </c>
+      <c r="P7">
+        <v>0.181</v>
+      </c>
+      <c r="Q7">
+        <v>0.04491315136476427</v>
+      </c>
+      <c r="R7">
+        <v>-0.03351851851851852</v>
+      </c>
+      <c r="S7">
+        <v>0.08600000000000002</v>
+      </c>
+      <c r="T7">
+        <v>0.3220973782771536</v>
+      </c>
+      <c r="U7">
+        <v>1.31</v>
+      </c>
+      <c r="V7">
+        <v>0.3250620347394541</v>
+      </c>
+      <c r="W7">
+        <v>-0.3439490445859873</v>
+      </c>
+      <c r="X7">
+        <v>0.0566083256279756</v>
+      </c>
+      <c r="Y7">
+        <v>-0.4005573702139629</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>-0.3983903420523139</v>
+      </c>
+      <c r="AB7">
+        <v>0.0566083256279756</v>
+      </c>
+      <c r="AC7">
+        <v>-0.4549986676802895</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>-1.31</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>-0.4816176470588235</v>
+      </c>
+      <c r="AK7">
+        <v>-0.1457174638487208</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Magnetic North Acquisition Corp. (TSXV:MNC)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="K7">
-        <v>1.14</v>
-      </c>
-      <c r="M7">
-        <v>-0</v>
-      </c>
-      <c r="N7">
-        <v>-0</v>
-      </c>
-      <c r="O7">
-        <v>-0</v>
-      </c>
-      <c r="P7">
-        <v>-0</v>
-      </c>
-      <c r="Q7">
-        <v>-0</v>
-      </c>
-      <c r="R7">
-        <v>-0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>-0.1341176470588235</v>
-      </c>
-      <c r="X7">
-        <v>0.3035139318924768</v>
-      </c>
-      <c r="Y7">
-        <v>-0.4376315789513003</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>-0.4285048905449464</v>
-      </c>
-      <c r="AB7">
-        <v>0.0644571768007775</v>
-      </c>
-      <c r="AC7">
-        <v>-0.4929620673457239</v>
-      </c>
-      <c r="AD7">
-        <v>12.8</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>12.8</v>
-      </c>
-      <c r="AG7">
-        <v>12.8</v>
-      </c>
-      <c r="AH7">
-        <v>0.9215262778977682</v>
-      </c>
-      <c r="AI7">
-        <v>1.987577639751553</v>
-      </c>
-      <c r="AJ7">
-        <v>0.9215262778977682</v>
-      </c>
-      <c r="AK7">
-        <v>1.987577639751553</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>-0.003</v>
-      </c>
-      <c r="AN7">
-        <v>-6.994535519125683</v>
-      </c>
-      <c r="AP7">
-        <v>-6.994535519125683</v>
-      </c>
-      <c r="AQ7">
-        <v>613.3333333333334</v>
+      <c r="K8">
+        <v>-7.32</v>
+      </c>
+      <c r="M8">
+        <v>0.322</v>
+      </c>
+      <c r="N8">
+        <v>0.1106529209621993</v>
+      </c>
+      <c r="O8">
+        <v>-0.04398907103825136</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0.322</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>0.007</v>
+      </c>
+      <c r="V8">
+        <v>0.002405498281786942</v>
+      </c>
+      <c r="W8">
+        <v>1.150943396226415</v>
+      </c>
+      <c r="X8">
+        <v>0.1150820546229264</v>
+      </c>
+      <c r="Y8">
+        <v>1.035861341603489</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>-0.5636645962732919</v>
+      </c>
+      <c r="AB8">
+        <v>0.05319362658408019</v>
+      </c>
+      <c r="AC8">
+        <v>-0.6168582228573721</v>
+      </c>
+      <c r="AD8">
+        <v>13</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>13</v>
+      </c>
+      <c r="AG8">
+        <v>12.993</v>
+      </c>
+      <c r="AH8">
+        <v>0.8170961659333752</v>
+      </c>
+      <c r="AI8">
+        <v>-18.57142857142859</v>
+      </c>
+      <c r="AJ8">
+        <v>0.8170156574231278</v>
+      </c>
+      <c r="AK8">
+        <v>-18.37765205091941</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>-0.004</v>
+      </c>
+      <c r="AN8">
+        <v>-3.581267217630854</v>
+      </c>
+      <c r="AP8">
+        <v>-3.579338842975207</v>
+      </c>
+      <c r="AQ8">
+        <v>907.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>IC Capitalight Corp. (CNSX:IC)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G9">
+        <v>0.05447470817120628</v>
+      </c>
+      <c r="H9">
+        <v>-1.027237354085603</v>
+      </c>
+      <c r="I9">
+        <v>-1.140077821011673</v>
+      </c>
+      <c r="J9">
+        <v>-1.140077821011673</v>
+      </c>
+      <c r="K9">
+        <v>-0.716</v>
+      </c>
+      <c r="L9">
+        <v>-1.392996108949416</v>
+      </c>
+      <c r="M9">
+        <v>-0</v>
+      </c>
+      <c r="N9">
+        <v>-0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>-0</v>
+      </c>
+      <c r="Q9">
+        <v>-0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0.903</v>
+      </c>
+      <c r="V9">
+        <v>0.4219626168224299</v>
+      </c>
+      <c r="W9">
+        <v>-0.5114285714285715</v>
+      </c>
+      <c r="X9">
+        <v>0.05679181795512367</v>
+      </c>
+      <c r="Y9">
+        <v>-0.5682203893836951</v>
+      </c>
+      <c r="AB9">
+        <v>0.05655055051795606</v>
+      </c>
+      <c r="AD9">
+        <v>0.03</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0.03</v>
+      </c>
+      <c r="AG9">
+        <v>-0.873</v>
+      </c>
+      <c r="AH9">
+        <v>0.01382488479262673</v>
+      </c>
+      <c r="AI9">
+        <v>0.04054054054054054</v>
+      </c>
+      <c r="AJ9">
+        <v>-0.6890292028413575</v>
+      </c>
+      <c r="AK9">
+        <v>5.355828220858895</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>-0.078</v>
+      </c>
+      <c r="AN9">
+        <v>-0.05181347150259068</v>
+      </c>
+      <c r="AP9">
+        <v>1.507772020725389</v>
+      </c>
+      <c r="AQ9">
+        <v>7.512820512820513</v>
       </c>
     </row>
   </sheetData>
